--- a/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230701_20240101.xlsx
+++ b/MOMENTUM_DB_2 copy/Stocks/Nifty_500_2025_Apr_20_stocks_results/momentum_20230701_20240101.xlsx
@@ -921,37 +921,37 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>70.96774193548387</v>
+        <v>58.53658536585365</v>
       </c>
       <c r="C12" t="n">
-        <v>29.03225806451613</v>
+        <v>40.65040650406504</v>
       </c>
       <c r="D12" t="n">
-        <v>76.73896198683173</v>
+        <v>112.2202837603294</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>INE903U01023</t>
+          <t>INE040H01021</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="G12" t="n">
-        <v>-41.93548387096774</v>
+        <v>-17.88617886178861</v>
       </c>
       <c r="H12" t="n">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="I12" t="n">
         <v>56</v>
       </c>
       <c r="J12" t="n">
-        <v>877.35</v>
+        <v>38.2</v>
       </c>
       <c r="K12" t="n">
         <v>11</v>
@@ -965,37 +965,37 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>SIGNATURE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.53658536585365</v>
+        <v>70.96774193548387</v>
       </c>
       <c r="C13" t="n">
-        <v>40.65040650406504</v>
+        <v>29.03225806451613</v>
       </c>
       <c r="D13" t="n">
-        <v>112.2202837603294</v>
+        <v>76.73896198683173</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>INE040H01021</t>
+          <t>INE903U01023</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="G13" t="n">
-        <v>-17.88617886178861</v>
+        <v>-41.93548387096774</v>
       </c>
       <c r="H13" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I13" t="n">
         <v>56</v>
       </c>
       <c r="J13" t="n">
-        <v>38.2</v>
+        <v>877.35</v>
       </c>
       <c r="K13" t="n">
         <v>12</v>
